--- a/ATIVA-ER_PT_April 13_2026.xlsx
+++ b/ATIVA-ER_PT_April 13_2026.xlsx
@@ -1,14 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://myoffice.accenture.com/personal/sofia_lopes_accenture_com/Documents/Mestrado/MEU/Project/MEU-project/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_DFA6C516AFFB0BBDC9117B191BBA7864AE904E4A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D31C7E9-FECA-4D32-AA52-CB66B1EE26F7}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet0" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Sheet0!$A$1:$AR$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet0!$A$1:$AR$61</definedName>
   </definedNames>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="QG8SR3N2UvHM7ihPNVXu2ls+WO/tZ0NpZ8ak1IGLrSg="/>
@@ -18,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2839" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2624" uniqueCount="261">
   <si>
     <t>Diagnosis</t>
   </si>
@@ -773,9 +783,6 @@
   </si>
   <si>
     <t>On demand support,Tailored answers,Unbiased answers</t>
-  </si>
-  <si>
-    <t>Sub-Saharan Africa - PALOP</t>
   </si>
   <si>
     <t>Tailored answers,More company,Unbiased answers</t>
@@ -826,20 +833,21 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
@@ -850,7 +858,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -860,40 +868,50 @@
     </fill>
   </fills>
   <borders count="2">
-    <border/>
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1083,23 +1101,23 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AR972"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="35.0"/>
-    <col customWidth="1" min="2" max="2" width="36.86"/>
-    <col customWidth="1" min="3" max="4" width="34.0"/>
-    <col customWidth="1" min="5" max="44" width="8.71"/>
+    <col min="1" max="1" width="35" customWidth="1"/>
+    <col min="2" max="2" width="36.88671875" customWidth="1"/>
+    <col min="3" max="4" width="34" customWidth="1"/>
+    <col min="5" max="44" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:44" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1233,7 +1251,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:44" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>42</v>
       </c>
@@ -1365,7 +1383,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:44" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>80</v>
       </c>
@@ -1403,7 +1421,7 @@
         <v>82</v>
       </c>
       <c r="M3" s="3">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>83</v>
@@ -1499,7 +1517,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:44" ht="144" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>80</v>
       </c>
@@ -1537,7 +1555,7 @@
         <v>96</v>
       </c>
       <c r="M4" s="3">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>97</v>
@@ -1633,7 +1651,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:44" ht="72" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>103</v>
       </c>
@@ -1671,7 +1689,7 @@
         <v>81</v>
       </c>
       <c r="M5" s="3">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>97</v>
@@ -1767,7 +1785,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:44" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>80</v>
       </c>
@@ -1805,7 +1823,7 @@
         <v>82</v>
       </c>
       <c r="M6" s="3">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>83</v>
@@ -1901,7 +1919,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:44" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>80</v>
       </c>
@@ -1939,7 +1957,7 @@
         <v>82</v>
       </c>
       <c r="M7" s="3">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>83</v>
@@ -2035,7 +2053,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:44" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>80</v>
       </c>
@@ -2073,7 +2091,7 @@
         <v>82</v>
       </c>
       <c r="M8" s="3">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>83</v>
@@ -2169,7 +2187,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:44" ht="216" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>80</v>
       </c>
@@ -2207,7 +2225,7 @@
         <v>82</v>
       </c>
       <c r="M9" s="3">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>97</v>
@@ -2303,7 +2321,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:44" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>80</v>
       </c>
@@ -2341,7 +2359,7 @@
         <v>82</v>
       </c>
       <c r="M10" s="3">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>97</v>
@@ -2437,7 +2455,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:44" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>80</v>
       </c>
@@ -2475,7 +2493,7 @@
         <v>82</v>
       </c>
       <c r="M11" s="3">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>83</v>
@@ -2571,7 +2589,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:44" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>80</v>
       </c>
@@ -2609,7 +2627,7 @@
         <v>82</v>
       </c>
       <c r="M12" s="3">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="N12" s="2" t="s">
         <v>97</v>
@@ -2705,7 +2723,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:44" ht="72" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>103</v>
       </c>
@@ -2743,7 +2761,7 @@
         <v>81</v>
       </c>
       <c r="M13" s="3">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="N13" s="2" t="s">
         <v>97</v>
@@ -2839,7 +2857,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:44" ht="216" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>80</v>
       </c>
@@ -2877,7 +2895,7 @@
         <v>82</v>
       </c>
       <c r="M14" s="3">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="N14" s="2" t="s">
         <v>97</v>
@@ -2973,7 +2991,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:44" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>80</v>
       </c>
@@ -3011,7 +3029,7 @@
         <v>143</v>
       </c>
       <c r="M15" s="3">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="N15" s="2" t="s">
         <v>83</v>
@@ -3107,7 +3125,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:44" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>80</v>
       </c>
@@ -3145,7 +3163,7 @@
         <v>82</v>
       </c>
       <c r="M16" s="3">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="N16" s="2" t="s">
         <v>97</v>
@@ -3241,7 +3259,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="17" ht="15.75" customHeight="1">
+    <row r="17" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>80</v>
       </c>
@@ -3279,7 +3297,7 @@
         <v>82</v>
       </c>
       <c r="M17" s="3">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="N17" s="2" t="s">
         <v>97</v>
@@ -3375,7 +3393,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="18" ht="15.75" customHeight="1">
+    <row r="18" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>80</v>
       </c>
@@ -3413,7 +3431,7 @@
         <v>82</v>
       </c>
       <c r="M18" s="3">
-        <v>19.0</v>
+        <v>19</v>
       </c>
       <c r="N18" s="2" t="s">
         <v>97</v>
@@ -3509,7 +3527,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="19" ht="15.75" customHeight="1">
+    <row r="19" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>80</v>
       </c>
@@ -3547,7 +3565,7 @@
         <v>143</v>
       </c>
       <c r="M19" s="3">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="N19" s="2" t="s">
         <v>97</v>
@@ -3643,7 +3661,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="20" ht="15.75" customHeight="1">
+    <row r="20" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>80</v>
       </c>
@@ -3681,7 +3699,7 @@
         <v>82</v>
       </c>
       <c r="M20" s="3">
-        <v>19.0</v>
+        <v>19</v>
       </c>
       <c r="N20" s="2" t="s">
         <v>97</v>
@@ -3777,7 +3795,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
+    <row r="21" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>80</v>
       </c>
@@ -3815,7 +3833,7 @@
         <v>82</v>
       </c>
       <c r="M21" s="3">
-        <v>19.0</v>
+        <v>19</v>
       </c>
       <c r="N21" s="2" t="s">
         <v>97</v>
@@ -3911,7 +3929,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
+    <row r="22" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>80</v>
       </c>
@@ -3949,7 +3967,7 @@
         <v>96</v>
       </c>
       <c r="M22" s="3">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="N22" s="2" t="s">
         <v>97</v>
@@ -4045,7 +4063,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="23" ht="15.75" customHeight="1">
+    <row r="23" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>80</v>
       </c>
@@ -4083,7 +4101,7 @@
         <v>82</v>
       </c>
       <c r="M23" s="3">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="N23" s="2" t="s">
         <v>83</v>
@@ -4179,7 +4197,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="24" ht="15.75" customHeight="1">
+    <row r="24" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>80</v>
       </c>
@@ -4217,7 +4235,7 @@
         <v>166</v>
       </c>
       <c r="M24" s="3">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="N24" s="2" t="s">
         <v>83</v>
@@ -4313,7 +4331,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="25" ht="15.75" customHeight="1">
+    <row r="25" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>80</v>
       </c>
@@ -4351,7 +4369,7 @@
         <v>82</v>
       </c>
       <c r="M25" s="3">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="N25" s="2" t="s">
         <v>97</v>
@@ -4447,7 +4465,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="26" ht="15.75" customHeight="1">
+    <row r="26" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>123</v>
       </c>
@@ -4485,7 +4503,7 @@
         <v>81</v>
       </c>
       <c r="M26" s="3">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="N26" s="2" t="s">
         <v>97</v>
@@ -4581,7 +4599,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="27" ht="15.75" customHeight="1">
+    <row r="27" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>80</v>
       </c>
@@ -4619,7 +4637,7 @@
         <v>176</v>
       </c>
       <c r="M27" s="3">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="N27" s="2" t="s">
         <v>97</v>
@@ -4715,7 +4733,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="28" ht="15.75" customHeight="1">
+    <row r="28" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>80</v>
       </c>
@@ -4753,7 +4771,7 @@
         <v>82</v>
       </c>
       <c r="M28" s="3">
-        <v>53.0</v>
+        <v>53</v>
       </c>
       <c r="N28" s="2" t="s">
         <v>97</v>
@@ -4849,7 +4867,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="29" ht="15.75" customHeight="1">
+    <row r="29" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>103</v>
       </c>
@@ -4887,7 +4905,7 @@
         <v>81</v>
       </c>
       <c r="M29" s="3">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="N29" s="2" t="s">
         <v>97</v>
@@ -4983,7 +5001,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="30" ht="15.75" customHeight="1">
+    <row r="30" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>143</v>
       </c>
@@ -5021,7 +5039,7 @@
         <v>81</v>
       </c>
       <c r="M30" s="3">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="N30" s="2" t="s">
         <v>97</v>
@@ -5117,7 +5135,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="31" ht="15.75" customHeight="1">
+    <row r="31" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>80</v>
       </c>
@@ -5155,7 +5173,7 @@
         <v>143</v>
       </c>
       <c r="M31" s="3">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="N31" s="2" t="s">
         <v>97</v>
@@ -5251,7 +5269,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="32" ht="15.75" customHeight="1">
+    <row r="32" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>80</v>
       </c>
@@ -5289,7 +5307,7 @@
         <v>82</v>
       </c>
       <c r="M32" s="3">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="N32" s="2" t="s">
         <v>97</v>
@@ -5385,7 +5403,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="33" ht="15.75" customHeight="1">
+    <row r="33" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>80</v>
       </c>
@@ -5423,7 +5441,7 @@
         <v>82</v>
       </c>
       <c r="M33" s="3">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="N33" s="2" t="s">
         <v>83</v>
@@ -5519,7 +5537,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="34" ht="15.75" customHeight="1">
+    <row r="34" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>80</v>
       </c>
@@ -5557,7 +5575,7 @@
         <v>82</v>
       </c>
       <c r="M34" s="3">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="N34" s="2" t="s">
         <v>97</v>
@@ -5653,18 +5671,18 @@
         <v>81</v>
       </c>
     </row>
-    <row r="35" ht="15.75" customHeight="1">
+    <row r="35" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>96</v>
+        <v>176</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>199</v>
+        <v>81</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>200</v>
+        <v>81</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>81</v>
@@ -5682,7 +5700,7 @@
         <v>81</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>80</v>
+        <v>143</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>81</v>
@@ -5691,13 +5709,13 @@
         <v>81</v>
       </c>
       <c r="M35" s="3">
-        <v>21.0</v>
+        <v>22</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="P35" s="2" t="s">
         <v>81</v>
@@ -5712,7 +5730,7 @@
         <v>81</v>
       </c>
       <c r="T35" s="2" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="U35" s="2" t="s">
         <v>88</v>
@@ -5730,7 +5748,7 @@
         <v>81</v>
       </c>
       <c r="Z35" s="2" t="s">
-        <v>81</v>
+        <v>145</v>
       </c>
       <c r="AA35" s="2" t="s">
         <v>81</v>
@@ -5739,13 +5757,13 @@
         <v>81</v>
       </c>
       <c r="AC35" s="2" t="s">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="AD35" s="2" t="s">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AE35" s="2" t="s">
-        <v>81</v>
+        <v>140</v>
       </c>
       <c r="AF35" s="2" t="s">
         <v>81</v>
@@ -5757,7 +5775,7 @@
         <v>81</v>
       </c>
       <c r="AI35" s="2" t="s">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AJ35" s="2" t="s">
         <v>81</v>
@@ -5787,45 +5805,45 @@
         <v>81</v>
       </c>
     </row>
-    <row r="36" ht="15.75" customHeight="1">
+    <row r="36" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J36" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="I36" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="J36" s="2" t="s">
-        <v>81</v>
-      </c>
       <c r="K36" s="2" t="s">
         <v>81</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M36" s="3">
-        <v>19.0</v>
+        <v>23</v>
       </c>
       <c r="N36" s="2" t="s">
         <v>97</v>
@@ -5846,7 +5864,7 @@
         <v>81</v>
       </c>
       <c r="T36" s="2" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="U36" s="2" t="s">
         <v>88</v>
@@ -5858,13 +5876,13 @@
         <v>81</v>
       </c>
       <c r="X36" s="2" t="s">
-        <v>90</v>
+        <v>177</v>
       </c>
       <c r="Y36" s="2" t="s">
         <v>81</v>
       </c>
       <c r="Z36" s="2" t="s">
-        <v>81</v>
+        <v>186</v>
       </c>
       <c r="AA36" s="2" t="s">
         <v>81</v>
@@ -5873,10 +5891,10 @@
         <v>81</v>
       </c>
       <c r="AC36" s="2" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AD36" s="2" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AE36" s="2" t="s">
         <v>81</v>
@@ -5885,13 +5903,13 @@
         <v>81</v>
       </c>
       <c r="AG36" s="2" t="s">
-        <v>81</v>
+        <v>203</v>
       </c>
       <c r="AH36" s="2" t="s">
         <v>81</v>
       </c>
       <c r="AI36" s="2" t="s">
-        <v>81</v>
+        <v>131</v>
       </c>
       <c r="AJ36" s="2" t="s">
         <v>81</v>
@@ -5900,7 +5918,7 @@
         <v>81</v>
       </c>
       <c r="AL36" s="2" t="s">
-        <v>81</v>
+        <v>141</v>
       </c>
       <c r="AM36" s="2" t="s">
         <v>81</v>
@@ -5921,7 +5939,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="37" ht="15.75" customHeight="1">
+    <row r="37" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>80</v>
       </c>
@@ -5959,7 +5977,7 @@
         <v>82</v>
       </c>
       <c r="M37" s="3">
-        <v>21.0</v>
+        <v>22</v>
       </c>
       <c r="N37" s="2" t="s">
         <v>97</v>
@@ -5998,7 +6016,7 @@
         <v>81</v>
       </c>
       <c r="Z37" s="2" t="s">
-        <v>109</v>
+        <v>194</v>
       </c>
       <c r="AA37" s="2" t="s">
         <v>81</v>
@@ -6007,10 +6025,10 @@
         <v>81</v>
       </c>
       <c r="AC37" s="2" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AD37" s="2" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AE37" s="2" t="s">
         <v>81</v>
@@ -6019,13 +6037,13 @@
         <v>81</v>
       </c>
       <c r="AG37" s="2" t="s">
-        <v>81</v>
+        <v>204</v>
       </c>
       <c r="AH37" s="2" t="s">
         <v>81</v>
       </c>
       <c r="AI37" s="2" t="s">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AJ37" s="2" t="s">
         <v>81</v>
@@ -6055,18 +6073,18 @@
         <v>81</v>
       </c>
     </row>
-    <row r="38" ht="15.75" customHeight="1">
+    <row r="38" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>176</v>
+        <v>96</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>81</v>
+        <v>205</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>81</v>
+        <v>200</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>81</v>
@@ -6084,7 +6102,7 @@
         <v>81</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>143</v>
+        <v>80</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>81</v>
@@ -6093,13 +6111,13 @@
         <v>81</v>
       </c>
       <c r="M38" s="3">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="N38" s="2" t="s">
         <v>83</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="P38" s="2" t="s">
         <v>81</v>
@@ -6132,34 +6150,34 @@
         <v>81</v>
       </c>
       <c r="Z38" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="AA38" s="2" t="s">
         <v>81</v>
       </c>
       <c r="AB38" s="2" t="s">
-        <v>81</v>
+        <v>121</v>
       </c>
       <c r="AC38" s="2" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="AD38" s="2" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="AE38" s="2" t="s">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="AF38" s="2" t="s">
         <v>81</v>
       </c>
       <c r="AG38" s="2" t="s">
-        <v>81</v>
+        <v>206</v>
       </c>
       <c r="AH38" s="2" t="s">
-        <v>81</v>
+        <v>207</v>
       </c>
       <c r="AI38" s="2" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="AJ38" s="2" t="s">
         <v>81</v>
@@ -6168,10 +6186,10 @@
         <v>81</v>
       </c>
       <c r="AL38" s="2" t="s">
-        <v>81</v>
+        <v>208</v>
       </c>
       <c r="AM38" s="2" t="s">
-        <v>81</v>
+        <v>209</v>
       </c>
       <c r="AN38" s="2" t="s">
         <v>81</v>
@@ -6189,9 +6207,9 @@
         <v>81</v>
       </c>
     </row>
-    <row r="39" ht="15.75" customHeight="1">
+    <row r="39" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>143</v>
+        <v>80</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>81</v>
@@ -6203,13 +6221,13 @@
         <v>81</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>199</v>
+        <v>81</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>201</v>
+        <v>81</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>202</v>
+        <v>81</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>81</v>
@@ -6218,22 +6236,22 @@
         <v>81</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K39" s="2" t="s">
         <v>81</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>81</v>
+        <v>176</v>
       </c>
       <c r="M39" s="3">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="P39" s="2" t="s">
         <v>81</v>
@@ -6260,13 +6278,13 @@
         <v>81</v>
       </c>
       <c r="X39" s="2" t="s">
-        <v>177</v>
+        <v>90</v>
       </c>
       <c r="Y39" s="2" t="s">
         <v>81</v>
       </c>
       <c r="Z39" s="2" t="s">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="AA39" s="2" t="s">
         <v>81</v>
@@ -6275,10 +6293,10 @@
         <v>81</v>
       </c>
       <c r="AC39" s="2" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="AD39" s="2" t="s">
-        <v>93</v>
+        <v>131</v>
       </c>
       <c r="AE39" s="2" t="s">
         <v>81</v>
@@ -6287,7 +6305,7 @@
         <v>81</v>
       </c>
       <c r="AG39" s="2" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="AH39" s="2" t="s">
         <v>81</v>
@@ -6302,7 +6320,7 @@
         <v>81</v>
       </c>
       <c r="AL39" s="2" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="AM39" s="2" t="s">
         <v>81</v>
@@ -6320,10 +6338,10 @@
         <v>81</v>
       </c>
       <c r="AR39" s="2" t="s">
-        <v>81</v>
+        <v>212</v>
       </c>
     </row>
-    <row r="40" ht="15.75" customHeight="1">
+    <row r="40" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>80</v>
       </c>
@@ -6361,13 +6379,13 @@
         <v>82</v>
       </c>
       <c r="M40" s="3">
-        <v>22.0</v>
+        <v>21</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="P40" s="2" t="s">
         <v>81</v>
@@ -6382,10 +6400,10 @@
         <v>81</v>
       </c>
       <c r="T40" s="2" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="U40" s="2" t="s">
-        <v>126</v>
+        <v>88</v>
       </c>
       <c r="V40" s="2" t="s">
         <v>89</v>
@@ -6400,7 +6418,7 @@
         <v>81</v>
       </c>
       <c r="Z40" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="AA40" s="2" t="s">
         <v>81</v>
@@ -6421,13 +6439,13 @@
         <v>81</v>
       </c>
       <c r="AG40" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AH40" s="2" t="s">
         <v>81</v>
       </c>
       <c r="AI40" s="2" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="AJ40" s="2" t="s">
         <v>81</v>
@@ -6436,7 +6454,7 @@
         <v>81</v>
       </c>
       <c r="AL40" s="2" t="s">
-        <v>81</v>
+        <v>213</v>
       </c>
       <c r="AM40" s="2" t="s">
         <v>81</v>
@@ -6457,18 +6475,18 @@
         <v>81</v>
       </c>
     </row>
-    <row r="41" ht="15.75" customHeight="1">
+    <row r="41" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>205</v>
+        <v>81</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>200</v>
+        <v>81</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>81</v>
@@ -6486,16 +6504,16 @@
         <v>81</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K41" s="2" t="s">
         <v>81</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>81</v>
+        <v>214</v>
       </c>
       <c r="M41" s="3">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="N41" s="2" t="s">
         <v>83</v>
@@ -6510,13 +6528,13 @@
         <v>85</v>
       </c>
       <c r="R41" s="2" t="s">
-        <v>86</v>
+        <v>152</v>
       </c>
       <c r="S41" s="2" t="s">
         <v>81</v>
       </c>
       <c r="T41" s="2" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="U41" s="2" t="s">
         <v>88</v>
@@ -6534,7 +6552,7 @@
         <v>81</v>
       </c>
       <c r="Z41" s="2" t="s">
-        <v>147</v>
+        <v>215</v>
       </c>
       <c r="AA41" s="2" t="s">
         <v>81</v>
@@ -6543,10 +6561,10 @@
         <v>121</v>
       </c>
       <c r="AC41" s="2" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="AD41" s="2" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="AE41" s="2" t="s">
         <v>81</v>
@@ -6555,10 +6573,10 @@
         <v>81</v>
       </c>
       <c r="AG41" s="2" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="AH41" s="2" t="s">
-        <v>207</v>
+        <v>81</v>
       </c>
       <c r="AI41" s="2" t="s">
         <v>131</v>
@@ -6570,10 +6588,10 @@
         <v>81</v>
       </c>
       <c r="AL41" s="2" t="s">
-        <v>208</v>
+        <v>141</v>
       </c>
       <c r="AM41" s="2" t="s">
-        <v>209</v>
+        <v>81</v>
       </c>
       <c r="AN41" s="2" t="s">
         <v>81</v>
@@ -6591,12 +6609,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="42" ht="15.75" customHeight="1">
+    <row r="42" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>80</v>
+        <v>123</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>81</v>
+        <v>217</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>81</v>
@@ -6620,16 +6638,16 @@
         <v>81</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>81</v>
+        <v>218</v>
       </c>
       <c r="K42" s="2" t="s">
         <v>81</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>176</v>
+        <v>81</v>
       </c>
       <c r="M42" s="3">
-        <v>23.0</v>
+        <v>22</v>
       </c>
       <c r="N42" s="2" t="s">
         <v>83</v>
@@ -6668,7 +6686,7 @@
         <v>81</v>
       </c>
       <c r="Z42" s="2" t="s">
-        <v>210</v>
+        <v>91</v>
       </c>
       <c r="AA42" s="2" t="s">
         <v>81</v>
@@ -6689,10 +6707,10 @@
         <v>81</v>
       </c>
       <c r="AG42" s="2" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="AH42" s="2" t="s">
-        <v>81</v>
+        <v>220</v>
       </c>
       <c r="AI42" s="2" t="s">
         <v>131</v>
@@ -6704,10 +6722,10 @@
         <v>81</v>
       </c>
       <c r="AL42" s="2" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="AM42" s="2" t="s">
-        <v>81</v>
+        <v>221</v>
       </c>
       <c r="AN42" s="2" t="s">
         <v>81</v>
@@ -6722,10 +6740,10 @@
         <v>81</v>
       </c>
       <c r="AR42" s="2" t="s">
-        <v>212</v>
+        <v>81</v>
       </c>
     </row>
-    <row r="43" ht="15.75" customHeight="1">
+    <row r="43" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>80</v>
       </c>
@@ -6760,10 +6778,10 @@
         <v>81</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>82</v>
+        <v>176</v>
       </c>
       <c r="M43" s="3">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="N43" s="2" t="s">
         <v>83</v>
@@ -6784,7 +6802,7 @@
         <v>81</v>
       </c>
       <c r="T43" s="2" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="U43" s="2" t="s">
         <v>88</v>
@@ -6802,7 +6820,7 @@
         <v>81</v>
       </c>
       <c r="Z43" s="2" t="s">
-        <v>197</v>
+        <v>109</v>
       </c>
       <c r="AA43" s="2" t="s">
         <v>81</v>
@@ -6811,10 +6829,10 @@
         <v>81</v>
       </c>
       <c r="AC43" s="2" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="AD43" s="2" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="AE43" s="2" t="s">
         <v>81</v>
@@ -6823,34 +6841,34 @@
         <v>81</v>
       </c>
       <c r="AG43" s="2" t="s">
-        <v>203</v>
+        <v>81</v>
       </c>
       <c r="AH43" s="2" t="s">
         <v>81</v>
       </c>
       <c r="AI43" s="2" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="AJ43" s="2" t="s">
-        <v>81</v>
+        <v>222</v>
       </c>
       <c r="AK43" s="2" t="s">
         <v>81</v>
       </c>
       <c r="AL43" s="2" t="s">
-        <v>213</v>
+        <v>81</v>
       </c>
       <c r="AM43" s="2" t="s">
         <v>81</v>
       </c>
       <c r="AN43" s="2" t="s">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AO43" s="2" t="s">
         <v>81</v>
       </c>
       <c r="AP43" s="2" t="s">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="AQ43" s="2" t="s">
         <v>81</v>
@@ -6859,7 +6877,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="44" ht="15.75" customHeight="1">
+    <row r="44" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>80</v>
       </c>
@@ -6894,13 +6912,13 @@
         <v>81</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>214</v>
+        <v>143</v>
       </c>
       <c r="M44" s="3">
-        <v>22.0</v>
+        <v>24</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="O44" s="2" t="s">
         <v>98</v>
@@ -6912,7 +6930,7 @@
         <v>85</v>
       </c>
       <c r="R44" s="2" t="s">
-        <v>152</v>
+        <v>223</v>
       </c>
       <c r="S44" s="2" t="s">
         <v>81</v>
@@ -6921,7 +6939,7 @@
         <v>99</v>
       </c>
       <c r="U44" s="2" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="V44" s="2" t="s">
         <v>89</v>
@@ -6936,7 +6954,7 @@
         <v>81</v>
       </c>
       <c r="Z44" s="2" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="AA44" s="2" t="s">
         <v>81</v>
@@ -6945,10 +6963,10 @@
         <v>121</v>
       </c>
       <c r="AC44" s="2" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="AD44" s="2" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="AE44" s="2" t="s">
         <v>81</v>
@@ -6957,13 +6975,13 @@
         <v>81</v>
       </c>
       <c r="AG44" s="2" t="s">
-        <v>216</v>
+        <v>81</v>
       </c>
       <c r="AH44" s="2" t="s">
         <v>81</v>
       </c>
       <c r="AI44" s="2" t="s">
-        <v>131</v>
+        <v>101</v>
       </c>
       <c r="AJ44" s="2" t="s">
         <v>81</v>
@@ -6972,7 +6990,7 @@
         <v>81</v>
       </c>
       <c r="AL44" s="2" t="s">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="AM44" s="2" t="s">
         <v>81</v>
@@ -6993,12 +7011,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="45" ht="15.75" customHeight="1">
+    <row r="45" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>123</v>
+        <v>80</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>217</v>
+        <v>81</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>81</v>
@@ -7022,16 +7040,16 @@
         <v>81</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>218</v>
+        <v>81</v>
       </c>
       <c r="K45" s="2" t="s">
         <v>81</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M45" s="3">
-        <v>22.0</v>
+        <v>21</v>
       </c>
       <c r="N45" s="2" t="s">
         <v>83</v>
@@ -7052,7 +7070,7 @@
         <v>81</v>
       </c>
       <c r="T45" s="2" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="U45" s="2" t="s">
         <v>88</v>
@@ -7064,13 +7082,13 @@
         <v>81</v>
       </c>
       <c r="X45" s="2" t="s">
-        <v>90</v>
+        <v>177</v>
       </c>
       <c r="Y45" s="2" t="s">
         <v>81</v>
       </c>
       <c r="Z45" s="2" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="AA45" s="2" t="s">
         <v>81</v>
@@ -7091,10 +7109,10 @@
         <v>81</v>
       </c>
       <c r="AG45" s="2" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="AH45" s="2" t="s">
-        <v>220</v>
+        <v>81</v>
       </c>
       <c r="AI45" s="2" t="s">
         <v>131</v>
@@ -7106,10 +7124,10 @@
         <v>81</v>
       </c>
       <c r="AL45" s="2" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="AM45" s="2" t="s">
-        <v>221</v>
+        <v>81</v>
       </c>
       <c r="AN45" s="2" t="s">
         <v>81</v>
@@ -7127,7 +7145,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="46" ht="15.75" customHeight="1">
+    <row r="46" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>80</v>
       </c>
@@ -7162,10 +7180,10 @@
         <v>81</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>176</v>
+        <v>82</v>
       </c>
       <c r="M46" s="3">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="N46" s="2" t="s">
         <v>83</v>
@@ -7186,10 +7204,10 @@
         <v>81</v>
       </c>
       <c r="T46" s="2" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="U46" s="2" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="V46" s="2" t="s">
         <v>89</v>
@@ -7213,7 +7231,7 @@
         <v>81</v>
       </c>
       <c r="AC46" s="2" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="AD46" s="2" t="s">
         <v>101</v>
@@ -7231,28 +7249,28 @@
         <v>81</v>
       </c>
       <c r="AI46" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="AJ46" s="2" t="s">
-        <v>222</v>
+        <v>81</v>
       </c>
       <c r="AK46" s="2" t="s">
         <v>81</v>
       </c>
       <c r="AL46" s="2" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AM46" s="2" t="s">
         <v>81</v>
       </c>
       <c r="AN46" s="2" t="s">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AO46" s="2" t="s">
         <v>81</v>
       </c>
       <c r="AP46" s="2" t="s">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AQ46" s="2" t="s">
         <v>81</v>
@@ -7261,48 +7279,48 @@
         <v>81</v>
       </c>
     </row>
-    <row r="47" ht="15.75" customHeight="1">
+    <row r="47" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J47" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H47" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="I47" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="J47" s="2" t="s">
-        <v>81</v>
-      </c>
       <c r="K47" s="2" t="s">
         <v>81</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>143</v>
+        <v>81</v>
       </c>
       <c r="M47" s="3">
-        <v>24.0</v>
+        <v>23</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="O47" s="2" t="s">
         <v>98</v>
@@ -7314,16 +7332,16 @@
         <v>85</v>
       </c>
       <c r="R47" s="2" t="s">
-        <v>223</v>
+        <v>86</v>
       </c>
       <c r="S47" s="2" t="s">
         <v>81</v>
       </c>
       <c r="T47" s="2" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="U47" s="2" t="s">
-        <v>126</v>
+        <v>88</v>
       </c>
       <c r="V47" s="2" t="s">
         <v>89</v>
@@ -7332,13 +7350,13 @@
         <v>81</v>
       </c>
       <c r="X47" s="2" t="s">
-        <v>90</v>
+        <v>226</v>
       </c>
       <c r="Y47" s="2" t="s">
         <v>81</v>
       </c>
       <c r="Z47" s="2" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="AA47" s="2" t="s">
         <v>81</v>
@@ -7350,10 +7368,10 @@
         <v>92</v>
       </c>
       <c r="AD47" s="2" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="AE47" s="2" t="s">
-        <v>81</v>
+        <v>228</v>
       </c>
       <c r="AF47" s="2" t="s">
         <v>81</v>
@@ -7365,7 +7383,7 @@
         <v>81</v>
       </c>
       <c r="AI47" s="2" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="AJ47" s="2" t="s">
         <v>81</v>
@@ -7374,7 +7392,7 @@
         <v>81</v>
       </c>
       <c r="AL47" s="2" t="s">
-        <v>81</v>
+        <v>229</v>
       </c>
       <c r="AM47" s="2" t="s">
         <v>81</v>
@@ -7395,7 +7413,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="48" ht="15.75" customHeight="1">
+    <row r="48" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>80</v>
       </c>
@@ -7433,7 +7451,7 @@
         <v>82</v>
       </c>
       <c r="M48" s="3">
-        <v>21.0</v>
+        <v>28</v>
       </c>
       <c r="N48" s="2" t="s">
         <v>83</v>
@@ -7454,7 +7472,7 @@
         <v>81</v>
       </c>
       <c r="T48" s="2" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="U48" s="2" t="s">
         <v>88</v>
@@ -7466,7 +7484,7 @@
         <v>81</v>
       </c>
       <c r="X48" s="2" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="Y48" s="2" t="s">
         <v>81</v>
@@ -7481,7 +7499,7 @@
         <v>81</v>
       </c>
       <c r="AC48" s="2" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="AD48" s="2" t="s">
         <v>131</v>
@@ -7493,10 +7511,10 @@
         <v>81</v>
       </c>
       <c r="AG48" s="2" t="s">
-        <v>211</v>
+        <v>123</v>
       </c>
       <c r="AH48" s="2" t="s">
-        <v>81</v>
+        <v>230</v>
       </c>
       <c r="AI48" s="2" t="s">
         <v>131</v>
@@ -7508,10 +7526,10 @@
         <v>81</v>
       </c>
       <c r="AL48" s="2" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="AM48" s="2" t="s">
-        <v>81</v>
+        <v>231</v>
       </c>
       <c r="AN48" s="2" t="s">
         <v>81</v>
@@ -7529,7 +7547,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="49" ht="15.75" customHeight="1">
+    <row r="49" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>80</v>
       </c>
@@ -7567,7 +7585,7 @@
         <v>82</v>
       </c>
       <c r="M49" s="3">
-        <v>21.0</v>
+        <v>30</v>
       </c>
       <c r="N49" s="2" t="s">
         <v>83</v>
@@ -7588,7 +7606,7 @@
         <v>81</v>
       </c>
       <c r="T49" s="2" t="s">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="U49" s="2" t="s">
         <v>126</v>
@@ -7600,19 +7618,19 @@
         <v>81</v>
       </c>
       <c r="X49" s="2" t="s">
-        <v>90</v>
+        <v>188</v>
       </c>
       <c r="Y49" s="2" t="s">
         <v>81</v>
       </c>
       <c r="Z49" s="2" t="s">
-        <v>109</v>
+        <v>232</v>
       </c>
       <c r="AA49" s="2" t="s">
         <v>81</v>
       </c>
       <c r="AB49" s="2" t="s">
-        <v>81</v>
+        <v>129</v>
       </c>
       <c r="AC49" s="2" t="s">
         <v>92</v>
@@ -7642,7 +7660,7 @@
         <v>81</v>
       </c>
       <c r="AL49" s="2" t="s">
-        <v>102</v>
+        <v>136</v>
       </c>
       <c r="AM49" s="2" t="s">
         <v>81</v>
@@ -7663,9 +7681,9 @@
         <v>81</v>
       </c>
     </row>
-    <row r="50" ht="15.75" customHeight="1">
+    <row r="50" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>225</v>
+        <v>80</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>81</v>
@@ -7677,13 +7695,13 @@
         <v>81</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>183</v>
+        <v>81</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>184</v>
+        <v>81</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>202</v>
+        <v>81</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>81</v>
@@ -7692,22 +7710,22 @@
         <v>81</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K50" s="2" t="s">
         <v>81</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>81</v>
+        <v>143</v>
       </c>
       <c r="M50" s="3">
-        <v>23.0</v>
+        <v>21</v>
       </c>
       <c r="N50" s="2" t="s">
         <v>83</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="P50" s="2" t="s">
         <v>81</v>
@@ -7722,7 +7740,7 @@
         <v>81</v>
       </c>
       <c r="T50" s="2" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="U50" s="2" t="s">
         <v>88</v>
@@ -7734,61 +7752,61 @@
         <v>81</v>
       </c>
       <c r="X50" s="2" t="s">
-        <v>226</v>
+        <v>90</v>
       </c>
       <c r="Y50" s="2" t="s">
         <v>81</v>
       </c>
       <c r="Z50" s="2" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="AA50" s="2" t="s">
         <v>81</v>
       </c>
       <c r="AB50" s="2" t="s">
-        <v>121</v>
+        <v>81</v>
       </c>
       <c r="AC50" s="2" t="s">
         <v>92</v>
       </c>
       <c r="AD50" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AE50" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="AF50" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="AG50" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="AH50" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="AI50" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="AE50" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="AF50" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AG50" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AH50" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AI50" s="2" t="s">
-        <v>131</v>
-      </c>
       <c r="AJ50" s="2" t="s">
-        <v>81</v>
+        <v>234</v>
       </c>
       <c r="AK50" s="2" t="s">
         <v>81</v>
       </c>
       <c r="AL50" s="2" t="s">
-        <v>229</v>
+        <v>81</v>
       </c>
       <c r="AM50" s="2" t="s">
         <v>81</v>
       </c>
       <c r="AN50" s="2" t="s">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AO50" s="2" t="s">
         <v>81</v>
       </c>
       <c r="AP50" s="2" t="s">
-        <v>81</v>
+        <v>125</v>
       </c>
       <c r="AQ50" s="2" t="s">
         <v>81</v>
@@ -7797,7 +7815,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="51" ht="15.75" customHeight="1">
+    <row r="51" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>80</v>
       </c>
@@ -7832,16 +7850,16 @@
         <v>81</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="M51" s="3">
-        <v>28.0</v>
+        <v>19</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="P51" s="2" t="s">
         <v>81</v>
@@ -7856,7 +7874,7 @@
         <v>81</v>
       </c>
       <c r="T51" s="2" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="U51" s="2" t="s">
         <v>88</v>
@@ -7868,22 +7886,22 @@
         <v>81</v>
       </c>
       <c r="X51" s="2" t="s">
-        <v>188</v>
+        <v>123</v>
       </c>
       <c r="Y51" s="2" t="s">
-        <v>81</v>
+        <v>235</v>
       </c>
       <c r="Z51" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="AA51" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="AB51" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="AC51" s="2" t="s">
         <v>109</v>
-      </c>
-      <c r="AA51" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AB51" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AC51" s="2" t="s">
-        <v>92</v>
       </c>
       <c r="AD51" s="2" t="s">
         <v>131</v>
@@ -7895,10 +7913,10 @@
         <v>81</v>
       </c>
       <c r="AG51" s="2" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="AH51" s="2" t="s">
-        <v>230</v>
+        <v>81</v>
       </c>
       <c r="AI51" s="2" t="s">
         <v>131</v>
@@ -7910,10 +7928,10 @@
         <v>81</v>
       </c>
       <c r="AL51" s="2" t="s">
-        <v>123</v>
+        <v>229</v>
       </c>
       <c r="AM51" s="2" t="s">
-        <v>231</v>
+        <v>81</v>
       </c>
       <c r="AN51" s="2" t="s">
         <v>81</v>
@@ -7928,10 +7946,10 @@
         <v>81</v>
       </c>
       <c r="AR51" s="2" t="s">
-        <v>81</v>
+        <v>236</v>
       </c>
     </row>
-    <row r="52" ht="15.75" customHeight="1">
+    <row r="52" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>80</v>
       </c>
@@ -7966,16 +7984,16 @@
         <v>81</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="M52" s="3">
-        <v>30.0</v>
+        <v>43</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="O52" s="2" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="P52" s="2" t="s">
         <v>81</v>
@@ -7990,43 +8008,43 @@
         <v>81</v>
       </c>
       <c r="T52" s="2" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="U52" s="2" t="s">
-        <v>126</v>
+        <v>88</v>
       </c>
       <c r="V52" s="2" t="s">
-        <v>89</v>
+        <v>179</v>
       </c>
       <c r="W52" s="2" t="s">
         <v>81</v>
       </c>
       <c r="X52" s="2" t="s">
-        <v>188</v>
+        <v>237</v>
       </c>
       <c r="Y52" s="2" t="s">
         <v>81</v>
       </c>
       <c r="Z52" s="2" t="s">
-        <v>232</v>
+        <v>123</v>
       </c>
       <c r="AA52" s="2" t="s">
-        <v>81</v>
+        <v>238</v>
       </c>
       <c r="AB52" s="2" t="s">
-        <v>129</v>
+        <v>81</v>
       </c>
       <c r="AC52" s="2" t="s">
         <v>92</v>
       </c>
       <c r="AD52" s="2" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="AE52" s="2" t="s">
-        <v>81</v>
+        <v>239</v>
       </c>
       <c r="AF52" s="2" t="s">
-        <v>81</v>
+        <v>240</v>
       </c>
       <c r="AG52" s="2" t="s">
         <v>81</v>
@@ -8035,28 +8053,28 @@
         <v>81</v>
       </c>
       <c r="AI52" s="2" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="AJ52" s="2" t="s">
-        <v>81</v>
+        <v>241</v>
       </c>
       <c r="AK52" s="2" t="s">
-        <v>81</v>
+        <v>242</v>
       </c>
       <c r="AL52" s="2" t="s">
-        <v>136</v>
+        <v>81</v>
       </c>
       <c r="AM52" s="2" t="s">
         <v>81</v>
       </c>
       <c r="AN52" s="2" t="s">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="AO52" s="2" t="s">
         <v>81</v>
       </c>
       <c r="AP52" s="2" t="s">
-        <v>81</v>
+        <v>125</v>
       </c>
       <c r="AQ52" s="2" t="s">
         <v>81</v>
@@ -8065,7 +8083,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="53" ht="15.75" customHeight="1">
+    <row r="53" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>80</v>
       </c>
@@ -8103,7 +8121,7 @@
         <v>143</v>
       </c>
       <c r="M53" s="3">
-        <v>21.0</v>
+        <v>20</v>
       </c>
       <c r="N53" s="2" t="s">
         <v>83</v>
@@ -8124,7 +8142,7 @@
         <v>81</v>
       </c>
       <c r="T53" s="2" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="U53" s="2" t="s">
         <v>88</v>
@@ -8142,7 +8160,7 @@
         <v>81</v>
       </c>
       <c r="Z53" s="2" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="AA53" s="2" t="s">
         <v>81</v>
@@ -8151,10 +8169,10 @@
         <v>81</v>
       </c>
       <c r="AC53" s="2" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="AD53" s="2" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="AE53" s="2" t="s">
         <v>81</v>
@@ -8163,34 +8181,34 @@
         <v>81</v>
       </c>
       <c r="AG53" s="2" t="s">
-        <v>81</v>
+        <v>146</v>
       </c>
       <c r="AH53" s="2" t="s">
         <v>81</v>
       </c>
       <c r="AI53" s="2" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="AJ53" s="2" t="s">
-        <v>234</v>
+        <v>81</v>
       </c>
       <c r="AK53" s="2" t="s">
         <v>81</v>
       </c>
       <c r="AL53" s="2" t="s">
-        <v>81</v>
+        <v>229</v>
       </c>
       <c r="AM53" s="2" t="s">
         <v>81</v>
       </c>
       <c r="AN53" s="2" t="s">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AO53" s="2" t="s">
         <v>81</v>
       </c>
       <c r="AP53" s="2" t="s">
-        <v>125</v>
+        <v>81</v>
       </c>
       <c r="AQ53" s="2" t="s">
         <v>81</v>
@@ -8199,51 +8217,51 @@
         <v>81</v>
       </c>
     </row>
-    <row r="54" ht="15.75" customHeight="1">
+    <row r="54" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J54" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="G54" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H54" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="I54" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="J54" s="2" t="s">
-        <v>81</v>
-      </c>
       <c r="K54" s="2" t="s">
         <v>81</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="M54" s="3">
-        <v>19.0</v>
+        <v>23</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="P54" s="2" t="s">
         <v>81</v>
@@ -8258,10 +8276,10 @@
         <v>81</v>
       </c>
       <c r="T54" s="2" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="U54" s="2" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="V54" s="2" t="s">
         <v>89</v>
@@ -8270,13 +8288,13 @@
         <v>81</v>
       </c>
       <c r="X54" s="2" t="s">
-        <v>123</v>
+        <v>90</v>
       </c>
       <c r="Y54" s="2" t="s">
-        <v>235</v>
+        <v>81</v>
       </c>
       <c r="Z54" s="2" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="AA54" s="2" t="s">
         <v>81</v>
@@ -8297,10 +8315,10 @@
         <v>81</v>
       </c>
       <c r="AG54" s="2" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="AH54" s="2" t="s">
-        <v>81</v>
+        <v>244</v>
       </c>
       <c r="AI54" s="2" t="s">
         <v>131</v>
@@ -8312,7 +8330,7 @@
         <v>81</v>
       </c>
       <c r="AL54" s="2" t="s">
-        <v>229</v>
+        <v>141</v>
       </c>
       <c r="AM54" s="2" t="s">
         <v>81</v>
@@ -8330,10 +8348,10 @@
         <v>81</v>
       </c>
       <c r="AR54" s="2" t="s">
-        <v>236</v>
+        <v>81</v>
       </c>
     </row>
-    <row r="55" ht="15.75" customHeight="1">
+    <row r="55" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>80</v>
       </c>
@@ -8368,16 +8386,16 @@
         <v>81</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="M55" s="3">
-        <v>43.0</v>
+        <v>22</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="P55" s="2" t="s">
         <v>81</v>
@@ -8392,28 +8410,28 @@
         <v>81</v>
       </c>
       <c r="T55" s="2" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="U55" s="2" t="s">
         <v>88</v>
       </c>
       <c r="V55" s="2" t="s">
-        <v>179</v>
+        <v>89</v>
       </c>
       <c r="W55" s="2" t="s">
         <v>81</v>
       </c>
       <c r="X55" s="2" t="s">
-        <v>237</v>
+        <v>90</v>
       </c>
       <c r="Y55" s="2" t="s">
         <v>81</v>
       </c>
       <c r="Z55" s="2" t="s">
-        <v>123</v>
+        <v>186</v>
       </c>
       <c r="AA55" s="2" t="s">
-        <v>238</v>
+        <v>81</v>
       </c>
       <c r="AB55" s="2" t="s">
         <v>81</v>
@@ -8425,10 +8443,10 @@
         <v>115</v>
       </c>
       <c r="AE55" s="2" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="AF55" s="2" t="s">
-        <v>240</v>
+        <v>81</v>
       </c>
       <c r="AG55" s="2" t="s">
         <v>81</v>
@@ -8437,13 +8455,13 @@
         <v>81</v>
       </c>
       <c r="AI55" s="2" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="AJ55" s="2" t="s">
-        <v>241</v>
+        <v>81</v>
       </c>
       <c r="AK55" s="2" t="s">
-        <v>242</v>
+        <v>81</v>
       </c>
       <c r="AL55" s="2" t="s">
         <v>81</v>
@@ -8452,13 +8470,13 @@
         <v>81</v>
       </c>
       <c r="AN55" s="2" t="s">
-        <v>113</v>
+        <v>81</v>
       </c>
       <c r="AO55" s="2" t="s">
         <v>81</v>
       </c>
       <c r="AP55" s="2" t="s">
-        <v>125</v>
+        <v>81</v>
       </c>
       <c r="AQ55" s="2" t="s">
         <v>81</v>
@@ -8467,7 +8485,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="56" ht="15.75" customHeight="1">
+    <row r="56" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>80</v>
       </c>
@@ -8502,10 +8520,10 @@
         <v>81</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>143</v>
+        <v>82</v>
       </c>
       <c r="M56" s="3">
-        <v>20.0</v>
+        <v>25</v>
       </c>
       <c r="N56" s="2" t="s">
         <v>83</v>
@@ -8526,10 +8544,10 @@
         <v>81</v>
       </c>
       <c r="T56" s="2" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="U56" s="2" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="V56" s="2" t="s">
         <v>89</v>
@@ -8544,7 +8562,7 @@
         <v>81</v>
       </c>
       <c r="Z56" s="2" t="s">
-        <v>243</v>
+        <v>109</v>
       </c>
       <c r="AA56" s="2" t="s">
         <v>81</v>
@@ -8553,25 +8571,25 @@
         <v>81</v>
       </c>
       <c r="AC56" s="2" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="AD56" s="2" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="AE56" s="2" t="s">
-        <v>81</v>
+        <v>246</v>
       </c>
       <c r="AF56" s="2" t="s">
         <v>81</v>
       </c>
       <c r="AG56" s="2" t="s">
-        <v>146</v>
+        <v>81</v>
       </c>
       <c r="AH56" s="2" t="s">
         <v>81</v>
       </c>
       <c r="AI56" s="2" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="AJ56" s="2" t="s">
         <v>81</v>
@@ -8580,7 +8598,7 @@
         <v>81</v>
       </c>
       <c r="AL56" s="2" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="AM56" s="2" t="s">
         <v>81</v>
@@ -8601,9 +8619,9 @@
         <v>81</v>
       </c>
     </row>
-    <row r="57" ht="15.75" customHeight="1">
+    <row r="57" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>143</v>
+        <v>80</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>81</v>
@@ -8615,13 +8633,13 @@
         <v>81</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>205</v>
+        <v>81</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>201</v>
+        <v>81</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>185</v>
+        <v>81</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>81</v>
@@ -8630,16 +8648,16 @@
         <v>81</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K57" s="2" t="s">
         <v>81</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="M57" s="3">
-        <v>23.0</v>
+        <v>25</v>
       </c>
       <c r="N57" s="2" t="s">
         <v>83</v>
@@ -8660,10 +8678,10 @@
         <v>81</v>
       </c>
       <c r="T57" s="2" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="U57" s="2" t="s">
-        <v>126</v>
+        <v>88</v>
       </c>
       <c r="V57" s="2" t="s">
         <v>89</v>
@@ -8678,7 +8696,7 @@
         <v>81</v>
       </c>
       <c r="Z57" s="2" t="s">
-        <v>109</v>
+        <v>233</v>
       </c>
       <c r="AA57" s="2" t="s">
         <v>81</v>
@@ -8690,7 +8708,7 @@
         <v>109</v>
       </c>
       <c r="AD57" s="2" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="AE57" s="2" t="s">
         <v>81</v>
@@ -8699,10 +8717,10 @@
         <v>81</v>
       </c>
       <c r="AG57" s="2" t="s">
-        <v>123</v>
+        <v>248</v>
       </c>
       <c r="AH57" s="2" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="AI57" s="2" t="s">
         <v>131</v>
@@ -8714,7 +8732,7 @@
         <v>81</v>
       </c>
       <c r="AL57" s="2" t="s">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AM57" s="2" t="s">
         <v>81</v>
@@ -8735,7 +8753,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="58" ht="15.75" customHeight="1">
+    <row r="58" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>80</v>
       </c>
@@ -8773,13 +8791,13 @@
         <v>82</v>
       </c>
       <c r="M58" s="3">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="P58" s="2" t="s">
         <v>81</v>
@@ -8794,7 +8812,7 @@
         <v>81</v>
       </c>
       <c r="T58" s="2" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="U58" s="2" t="s">
         <v>88</v>
@@ -8812,7 +8830,7 @@
         <v>81</v>
       </c>
       <c r="Z58" s="2" t="s">
-        <v>186</v>
+        <v>91</v>
       </c>
       <c r="AA58" s="2" t="s">
         <v>81</v>
@@ -8821,25 +8839,25 @@
         <v>81</v>
       </c>
       <c r="AC58" s="2" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="AD58" s="2" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="AE58" s="2" t="s">
-        <v>245</v>
+        <v>81</v>
       </c>
       <c r="AF58" s="2" t="s">
         <v>81</v>
       </c>
       <c r="AG58" s="2" t="s">
-        <v>81</v>
+        <v>123</v>
       </c>
       <c r="AH58" s="2" t="s">
-        <v>81</v>
+        <v>250</v>
       </c>
       <c r="AI58" s="2" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="AJ58" s="2" t="s">
         <v>81</v>
@@ -8848,10 +8866,10 @@
         <v>81</v>
       </c>
       <c r="AL58" s="2" t="s">
-        <v>81</v>
+        <v>251</v>
       </c>
       <c r="AM58" s="2" t="s">
-        <v>81</v>
+        <v>252</v>
       </c>
       <c r="AN58" s="2" t="s">
         <v>81</v>
@@ -8869,18 +8887,18 @@
         <v>81</v>
       </c>
     </row>
-    <row r="59" ht="15.75" customHeight="1">
+    <row r="59" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>199</v>
+        <v>81</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>200</v>
+        <v>81</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>81</v>
@@ -8898,16 +8916,16 @@
         <v>81</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K59" s="2" t="s">
         <v>81</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M59" s="3">
-        <v>20.0</v>
+        <v>22</v>
       </c>
       <c r="N59" s="2" t="s">
         <v>97</v>
@@ -8922,13 +8940,13 @@
         <v>85</v>
       </c>
       <c r="R59" s="2" t="s">
-        <v>246</v>
+        <v>86</v>
       </c>
       <c r="S59" s="2" t="s">
         <v>81</v>
       </c>
       <c r="T59" s="2" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="U59" s="2" t="s">
         <v>88</v>
@@ -8946,7 +8964,7 @@
         <v>81</v>
       </c>
       <c r="Z59" s="2" t="s">
-        <v>81</v>
+        <v>186</v>
       </c>
       <c r="AA59" s="2" t="s">
         <v>81</v>
@@ -8955,10 +8973,10 @@
         <v>81</v>
       </c>
       <c r="AC59" s="2" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AD59" s="2" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AE59" s="2" t="s">
         <v>81</v>
@@ -8967,16 +8985,16 @@
         <v>81</v>
       </c>
       <c r="AG59" s="2" t="s">
-        <v>81</v>
+        <v>253</v>
       </c>
       <c r="AH59" s="2" t="s">
         <v>81</v>
       </c>
       <c r="AI59" s="2" t="s">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AJ59" s="2" t="s">
-        <v>81</v>
+        <v>254</v>
       </c>
       <c r="AK59" s="2" t="s">
         <v>81</v>
@@ -8988,13 +9006,13 @@
         <v>81</v>
       </c>
       <c r="AN59" s="2" t="s">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AO59" s="2" t="s">
         <v>81</v>
       </c>
       <c r="AP59" s="2" t="s">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="AQ59" s="2" t="s">
         <v>81</v>
@@ -9003,7 +9021,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="60" ht="15.75" customHeight="1">
+    <row r="60" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>80</v>
       </c>
@@ -9041,13 +9059,13 @@
         <v>82</v>
       </c>
       <c r="M60" s="3">
-        <v>25.0</v>
+        <v>22</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="O60" s="2" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="P60" s="2" t="s">
         <v>81</v>
@@ -9065,7 +9083,7 @@
         <v>99</v>
       </c>
       <c r="U60" s="2" t="s">
-        <v>126</v>
+        <v>88</v>
       </c>
       <c r="V60" s="2" t="s">
         <v>89</v>
@@ -9074,13 +9092,13 @@
         <v>81</v>
       </c>
       <c r="X60" s="2" t="s">
-        <v>90</v>
+        <v>188</v>
       </c>
       <c r="Y60" s="2" t="s">
         <v>81</v>
       </c>
       <c r="Z60" s="2" t="s">
-        <v>109</v>
+        <v>243</v>
       </c>
       <c r="AA60" s="2" t="s">
         <v>81</v>
@@ -9089,13 +9107,13 @@
         <v>81</v>
       </c>
       <c r="AC60" s="2" t="s">
-        <v>92</v>
+        <v>255</v>
       </c>
       <c r="AD60" s="2" t="s">
         <v>115</v>
       </c>
       <c r="AE60" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AF60" s="2" t="s">
         <v>81</v>
@@ -9107,7 +9125,7 @@
         <v>81</v>
       </c>
       <c r="AI60" s="2" t="s">
-        <v>93</v>
+        <v>131</v>
       </c>
       <c r="AJ60" s="2" t="s">
         <v>81</v>
@@ -9116,10 +9134,10 @@
         <v>81</v>
       </c>
       <c r="AL60" s="2" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="AM60" s="2" t="s">
-        <v>81</v>
+        <v>257</v>
       </c>
       <c r="AN60" s="2" t="s">
         <v>81</v>
@@ -9137,7 +9155,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="61" ht="15.75" customHeight="1">
+    <row r="61" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>80</v>
       </c>
@@ -9172,10 +9190,10 @@
         <v>81</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>103</v>
+        <v>166</v>
       </c>
       <c r="M61" s="3">
-        <v>25.0</v>
+        <v>21</v>
       </c>
       <c r="N61" s="2" t="s">
         <v>83</v>
@@ -9196,7 +9214,7 @@
         <v>81</v>
       </c>
       <c r="T61" s="2" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="U61" s="2" t="s">
         <v>88</v>
@@ -9214,10 +9232,10 @@
         <v>81</v>
       </c>
       <c r="Z61" s="2" t="s">
-        <v>233</v>
+        <v>123</v>
       </c>
       <c r="AA61" s="2" t="s">
-        <v>81</v>
+        <v>258</v>
       </c>
       <c r="AB61" s="2" t="s">
         <v>81</v>
@@ -9235,10 +9253,10 @@
         <v>81</v>
       </c>
       <c r="AG61" s="2" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="AH61" s="2" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="AI61" s="2" t="s">
         <v>131</v>
@@ -9250,7 +9268,7 @@
         <v>81</v>
       </c>
       <c r="AL61" s="2" t="s">
-        <v>102</v>
+        <v>139</v>
       </c>
       <c r="AM61" s="2" t="s">
         <v>81</v>
@@ -9271,1592 +9289,926 @@
         <v>81</v>
       </c>
     </row>
-    <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F62" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="G62" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H62" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="I62" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="J62" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="K62" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="L62" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="M62" s="3">
-        <v>20.0</v>
-      </c>
-      <c r="N62" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="O62" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="P62" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q62" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="R62" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="S62" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="T62" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="U62" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="V62" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="W62" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="X62" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="Y62" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="Z62" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AA62" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AB62" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AC62" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AD62" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AE62" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AF62" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AG62" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AH62" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AI62" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AJ62" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AK62" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AL62" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AM62" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AN62" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AO62" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AP62" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AQ62" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AR62" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F63" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="G63" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H63" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="I63" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="J63" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="K63" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="L63" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="M63" s="3">
-        <v>22.0</v>
-      </c>
-      <c r="N63" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="O63" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="P63" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q63" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="R63" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="S63" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="T63" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="U63" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="V63" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="W63" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="X63" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="Y63" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="Z63" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="AA63" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AB63" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AC63" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="AD63" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="AE63" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AF63" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AG63" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AH63" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="AI63" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="AJ63" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AK63" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AL63" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="AM63" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="AN63" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AO63" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AP63" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AQ63" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AR63" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F64" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="G64" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H64" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="I64" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="J64" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="K64" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="L64" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="M64" s="3">
-        <v>22.0</v>
-      </c>
-      <c r="N64" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="O64" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="P64" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q64" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="R64" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="S64" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="T64" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="U64" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="V64" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="W64" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="X64" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="Y64" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="Z64" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="AA64" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AB64" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AC64" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD64" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="AE64" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AF64" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AG64" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="AH64" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AI64" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="AJ64" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="AK64" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AL64" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AM64" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AN64" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="AO64" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AP64" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="AQ64" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AR64" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F65" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="G65" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H65" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="I65" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="J65" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="K65" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="L65" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="M65" s="3">
-        <v>22.0</v>
-      </c>
-      <c r="N65" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="O65" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="P65" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q65" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="R65" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="S65" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="T65" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="U65" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="V65" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="W65" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="X65" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="Y65" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="Z65" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="AA65" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AB65" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AC65" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="AD65" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="AE65" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="AF65" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AG65" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AH65" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AI65" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="AJ65" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AK65" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AL65" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="AM65" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="AN65" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AO65" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AP65" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AQ65" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AR65" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F66" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="G66" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H66" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="I66" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="J66" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="K66" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="L66" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="M66" s="3">
-        <v>21.0</v>
-      </c>
-      <c r="N66" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="O66" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="P66" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q66" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="R66" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="S66" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="T66" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="U66" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="V66" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="W66" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="X66" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="Y66" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="Z66" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AA66" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="AB66" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AC66" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="AD66" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="AE66" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AF66" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AG66" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="AH66" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="AI66" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="AJ66" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AK66" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AL66" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="AM66" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AN66" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AO66" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AP66" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AQ66" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AR66" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="67" ht="15.75" customHeight="1"/>
-    <row r="68" ht="15.75" customHeight="1"/>
-    <row r="69" ht="15.75" customHeight="1"/>
-    <row r="70" ht="15.75" customHeight="1"/>
-    <row r="71" ht="15.75" customHeight="1"/>
-    <row r="72" ht="15.75" customHeight="1"/>
-    <row r="73" ht="15.75" customHeight="1"/>
-    <row r="74" ht="15.75" customHeight="1"/>
-    <row r="75" ht="15.75" customHeight="1"/>
-    <row r="76" ht="15.75" customHeight="1"/>
-    <row r="77" ht="15.75" customHeight="1"/>
-    <row r="78" ht="15.75" customHeight="1"/>
-    <row r="79" ht="15.75" customHeight="1"/>
-    <row r="80" ht="15.75" customHeight="1"/>
-    <row r="81" ht="15.75" customHeight="1"/>
-    <row r="82" ht="15.75" customHeight="1"/>
-    <row r="83" ht="15.75" customHeight="1"/>
-    <row r="84" ht="15.75" customHeight="1"/>
-    <row r="85" ht="15.75" customHeight="1"/>
-    <row r="86" ht="15.75" customHeight="1"/>
-    <row r="87" ht="15.75" customHeight="1"/>
-    <row r="88" ht="15.75" customHeight="1"/>
-    <row r="89" ht="15.75" customHeight="1"/>
-    <row r="90" ht="15.75" customHeight="1"/>
-    <row r="91" ht="15.75" customHeight="1"/>
-    <row r="92" ht="15.75" customHeight="1"/>
-    <row r="93" ht="15.75" customHeight="1"/>
-    <row r="94" ht="15.75" customHeight="1"/>
-    <row r="95" ht="15.75" customHeight="1"/>
-    <row r="96" ht="15.75" customHeight="1"/>
-    <row r="97" ht="15.75" customHeight="1"/>
-    <row r="98" ht="15.75" customHeight="1"/>
-    <row r="99" ht="15.75" customHeight="1"/>
-    <row r="100" ht="15.75" customHeight="1"/>
-    <row r="101" ht="15.75" customHeight="1"/>
-    <row r="102" ht="15.75" customHeight="1"/>
-    <row r="103" ht="15.75" customHeight="1"/>
-    <row r="104" ht="15.75" customHeight="1"/>
-    <row r="105" ht="15.75" customHeight="1"/>
-    <row r="106" ht="15.75" customHeight="1"/>
-    <row r="107" ht="15.75" customHeight="1"/>
-    <row r="108" ht="15.75" customHeight="1"/>
-    <row r="109" ht="15.75" customHeight="1"/>
-    <row r="110" ht="15.75" customHeight="1"/>
-    <row r="111" ht="15.75" customHeight="1"/>
-    <row r="112" ht="15.75" customHeight="1"/>
-    <row r="113" ht="15.75" customHeight="1"/>
-    <row r="114" ht="15.75" customHeight="1"/>
-    <row r="115" ht="15.75" customHeight="1"/>
-    <row r="116" ht="15.75" customHeight="1"/>
-    <row r="117" ht="15.75" customHeight="1"/>
-    <row r="118" ht="15.75" customHeight="1"/>
-    <row r="119" ht="15.75" customHeight="1"/>
-    <row r="120" ht="15.75" customHeight="1"/>
-    <row r="121" ht="15.75" customHeight="1"/>
-    <row r="122" ht="15.75" customHeight="1"/>
-    <row r="123" ht="15.75" customHeight="1"/>
-    <row r="124" ht="15.75" customHeight="1"/>
-    <row r="125" ht="15.75" customHeight="1"/>
-    <row r="126" ht="15.75" customHeight="1"/>
-    <row r="127" ht="15.75" customHeight="1"/>
-    <row r="128" ht="15.75" customHeight="1"/>
-    <row r="129" ht="15.75" customHeight="1"/>
-    <row r="130" ht="15.75" customHeight="1"/>
-    <row r="131" ht="15.75" customHeight="1"/>
-    <row r="132" ht="15.75" customHeight="1"/>
-    <row r="133" ht="15.75" customHeight="1"/>
-    <row r="134" ht="15.75" customHeight="1"/>
-    <row r="135" ht="15.75" customHeight="1"/>
-    <row r="136" ht="15.75" customHeight="1"/>
-    <row r="137" ht="15.75" customHeight="1"/>
-    <row r="138" ht="15.75" customHeight="1"/>
-    <row r="139" ht="15.75" customHeight="1"/>
-    <row r="140" ht="15.75" customHeight="1"/>
-    <row r="141" ht="15.75" customHeight="1"/>
-    <row r="142" ht="15.75" customHeight="1"/>
-    <row r="143" ht="15.75" customHeight="1"/>
-    <row r="144" ht="15.75" customHeight="1"/>
-    <row r="145" ht="15.75" customHeight="1"/>
-    <row r="146" ht="15.75" customHeight="1"/>
-    <row r="147" ht="15.75" customHeight="1"/>
-    <row r="148" ht="15.75" customHeight="1"/>
-    <row r="149" ht="15.75" customHeight="1"/>
-    <row r="150" ht="15.75" customHeight="1"/>
-    <row r="151" ht="15.75" customHeight="1"/>
-    <row r="152" ht="15.75" customHeight="1"/>
-    <row r="153" ht="15.75" customHeight="1"/>
-    <row r="154" ht="15.75" customHeight="1"/>
-    <row r="155" ht="15.75" customHeight="1"/>
-    <row r="156" ht="15.75" customHeight="1"/>
-    <row r="157" ht="15.75" customHeight="1"/>
-    <row r="158" ht="15.75" customHeight="1"/>
-    <row r="159" ht="15.75" customHeight="1"/>
-    <row r="160" ht="15.75" customHeight="1"/>
-    <row r="161" ht="15.75" customHeight="1"/>
-    <row r="162" ht="15.75" customHeight="1"/>
-    <row r="163" ht="15.75" customHeight="1"/>
-    <row r="164" ht="15.75" customHeight="1"/>
-    <row r="165" ht="15.75" customHeight="1"/>
-    <row r="166" ht="15.75" customHeight="1"/>
-    <row r="167" ht="15.75" customHeight="1"/>
-    <row r="168" ht="15.75" customHeight="1"/>
-    <row r="169" ht="15.75" customHeight="1"/>
-    <row r="170" ht="15.75" customHeight="1"/>
-    <row r="171" ht="15.75" customHeight="1"/>
-    <row r="172" ht="15.75" customHeight="1"/>
-    <row r="173" ht="15.75" customHeight="1"/>
-    <row r="174" ht="15.75" customHeight="1"/>
-    <row r="175" ht="15.75" customHeight="1"/>
-    <row r="176" ht="15.75" customHeight="1"/>
-    <row r="177" ht="15.75" customHeight="1"/>
-    <row r="178" ht="15.75" customHeight="1"/>
-    <row r="179" ht="15.75" customHeight="1"/>
-    <row r="180" ht="15.75" customHeight="1"/>
-    <row r="181" ht="15.75" customHeight="1"/>
-    <row r="182" ht="15.75" customHeight="1"/>
-    <row r="183" ht="15.75" customHeight="1"/>
-    <row r="184" ht="15.75" customHeight="1"/>
-    <row r="185" ht="15.75" customHeight="1"/>
-    <row r="186" ht="15.75" customHeight="1"/>
-    <row r="187" ht="15.75" customHeight="1"/>
-    <row r="188" ht="15.75" customHeight="1"/>
-    <row r="189" ht="15.75" customHeight="1"/>
-    <row r="190" ht="15.75" customHeight="1"/>
-    <row r="191" ht="15.75" customHeight="1"/>
-    <row r="192" ht="15.75" customHeight="1"/>
-    <row r="193" ht="15.75" customHeight="1"/>
-    <row r="194" ht="15.75" customHeight="1"/>
-    <row r="195" ht="15.75" customHeight="1"/>
-    <row r="196" ht="15.75" customHeight="1"/>
-    <row r="197" ht="15.75" customHeight="1"/>
-    <row r="198" ht="15.75" customHeight="1"/>
-    <row r="199" ht="15.75" customHeight="1"/>
-    <row r="200" ht="15.75" customHeight="1"/>
-    <row r="201" ht="15.75" customHeight="1"/>
-    <row r="202" ht="15.75" customHeight="1"/>
-    <row r="203" ht="15.75" customHeight="1"/>
-    <row r="204" ht="15.75" customHeight="1"/>
-    <row r="205" ht="15.75" customHeight="1"/>
-    <row r="206" ht="15.75" customHeight="1"/>
-    <row r="207" ht="15.75" customHeight="1"/>
-    <row r="208" ht="15.75" customHeight="1"/>
-    <row r="209" ht="15.75" customHeight="1"/>
-    <row r="210" ht="15.75" customHeight="1"/>
-    <row r="211" ht="15.75" customHeight="1"/>
-    <row r="212" ht="15.75" customHeight="1"/>
-    <row r="213" ht="15.75" customHeight="1"/>
-    <row r="214" ht="15.75" customHeight="1"/>
-    <row r="215" ht="15.75" customHeight="1"/>
-    <row r="216" ht="15.75" customHeight="1"/>
-    <row r="217" ht="15.75" customHeight="1"/>
-    <row r="218" ht="15.75" customHeight="1"/>
-    <row r="219" ht="15.75" customHeight="1"/>
-    <row r="220" ht="15.75" customHeight="1"/>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
-    <row r="225" ht="15.75" customHeight="1"/>
-    <row r="226" ht="15.75" customHeight="1"/>
-    <row r="227" ht="15.75" customHeight="1"/>
-    <row r="228" ht="15.75" customHeight="1"/>
-    <row r="229" ht="15.75" customHeight="1"/>
-    <row r="230" ht="15.75" customHeight="1"/>
-    <row r="231" ht="15.75" customHeight="1"/>
-    <row r="232" ht="15.75" customHeight="1"/>
-    <row r="233" ht="15.75" customHeight="1"/>
-    <row r="234" ht="15.75" customHeight="1"/>
-    <row r="235" ht="15.75" customHeight="1"/>
-    <row r="236" ht="15.75" customHeight="1"/>
-    <row r="237" ht="15.75" customHeight="1"/>
-    <row r="238" ht="15.75" customHeight="1"/>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1"/>
-    <row r="241" ht="15.75" customHeight="1"/>
-    <row r="242" ht="15.75" customHeight="1"/>
-    <row r="243" ht="15.75" customHeight="1"/>
-    <row r="244" ht="15.75" customHeight="1"/>
-    <row r="245" ht="15.75" customHeight="1"/>
-    <row r="246" ht="15.75" customHeight="1"/>
-    <row r="247" ht="15.75" customHeight="1"/>
-    <row r="248" ht="15.75" customHeight="1"/>
-    <row r="249" ht="15.75" customHeight="1"/>
-    <row r="250" ht="15.75" customHeight="1"/>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
-    <row r="808" ht="15.75" customHeight="1"/>
-    <row r="809" ht="15.75" customHeight="1"/>
-    <row r="810" ht="15.75" customHeight="1"/>
-    <row r="811" ht="15.75" customHeight="1"/>
-    <row r="812" ht="15.75" customHeight="1"/>
-    <row r="813" ht="15.75" customHeight="1"/>
-    <row r="814" ht="15.75" customHeight="1"/>
-    <row r="815" ht="15.75" customHeight="1"/>
-    <row r="816" ht="15.75" customHeight="1"/>
-    <row r="817" ht="15.75" customHeight="1"/>
-    <row r="818" ht="15.75" customHeight="1"/>
-    <row r="819" ht="15.75" customHeight="1"/>
-    <row r="820" ht="15.75" customHeight="1"/>
-    <row r="821" ht="15.75" customHeight="1"/>
-    <row r="822" ht="15.75" customHeight="1"/>
-    <row r="823" ht="15.75" customHeight="1"/>
-    <row r="824" ht="15.75" customHeight="1"/>
-    <row r="825" ht="15.75" customHeight="1"/>
-    <row r="826" ht="15.75" customHeight="1"/>
-    <row r="827" ht="15.75" customHeight="1"/>
-    <row r="828" ht="15.75" customHeight="1"/>
-    <row r="829" ht="15.75" customHeight="1"/>
-    <row r="830" ht="15.75" customHeight="1"/>
-    <row r="831" ht="15.75" customHeight="1"/>
-    <row r="832" ht="15.75" customHeight="1"/>
-    <row r="833" ht="15.75" customHeight="1"/>
-    <row r="834" ht="15.75" customHeight="1"/>
-    <row r="835" ht="15.75" customHeight="1"/>
-    <row r="836" ht="15.75" customHeight="1"/>
-    <row r="837" ht="15.75" customHeight="1"/>
-    <row r="838" ht="15.75" customHeight="1"/>
-    <row r="839" ht="15.75" customHeight="1"/>
-    <row r="840" ht="15.75" customHeight="1"/>
-    <row r="841" ht="15.75" customHeight="1"/>
-    <row r="842" ht="15.75" customHeight="1"/>
-    <row r="843" ht="15.75" customHeight="1"/>
-    <row r="844" ht="15.75" customHeight="1"/>
-    <row r="845" ht="15.75" customHeight="1"/>
-    <row r="846" ht="15.75" customHeight="1"/>
-    <row r="847" ht="15.75" customHeight="1"/>
-    <row r="848" ht="15.75" customHeight="1"/>
-    <row r="849" ht="15.75" customHeight="1"/>
-    <row r="850" ht="15.75" customHeight="1"/>
-    <row r="851" ht="15.75" customHeight="1"/>
-    <row r="852" ht="15.75" customHeight="1"/>
-    <row r="853" ht="15.75" customHeight="1"/>
-    <row r="854" ht="15.75" customHeight="1"/>
-    <row r="855" ht="15.75" customHeight="1"/>
-    <row r="856" ht="15.75" customHeight="1"/>
-    <row r="857" ht="15.75" customHeight="1"/>
-    <row r="858" ht="15.75" customHeight="1"/>
-    <row r="859" ht="15.75" customHeight="1"/>
-    <row r="860" ht="15.75" customHeight="1"/>
-    <row r="861" ht="15.75" customHeight="1"/>
-    <row r="862" ht="15.75" customHeight="1"/>
-    <row r="863" ht="15.75" customHeight="1"/>
-    <row r="864" ht="15.75" customHeight="1"/>
-    <row r="865" ht="15.75" customHeight="1"/>
-    <row r="866" ht="15.75" customHeight="1"/>
-    <row r="867" ht="15.75" customHeight="1"/>
-    <row r="868" ht="15.75" customHeight="1"/>
-    <row r="869" ht="15.75" customHeight="1"/>
-    <row r="870" ht="15.75" customHeight="1"/>
-    <row r="871" ht="15.75" customHeight="1"/>
-    <row r="872" ht="15.75" customHeight="1"/>
-    <row r="873" ht="15.75" customHeight="1"/>
-    <row r="874" ht="15.75" customHeight="1"/>
-    <row r="875" ht="15.75" customHeight="1"/>
-    <row r="876" ht="15.75" customHeight="1"/>
-    <row r="877" ht="15.75" customHeight="1"/>
-    <row r="878" ht="15.75" customHeight="1"/>
-    <row r="879" ht="15.75" customHeight="1"/>
-    <row r="880" ht="15.75" customHeight="1"/>
-    <row r="881" ht="15.75" customHeight="1"/>
-    <row r="882" ht="15.75" customHeight="1"/>
-    <row r="883" ht="15.75" customHeight="1"/>
-    <row r="884" ht="15.75" customHeight="1"/>
-    <row r="885" ht="15.75" customHeight="1"/>
-    <row r="886" ht="15.75" customHeight="1"/>
-    <row r="887" ht="15.75" customHeight="1"/>
-    <row r="888" ht="15.75" customHeight="1"/>
-    <row r="889" ht="15.75" customHeight="1"/>
-    <row r="890" ht="15.75" customHeight="1"/>
-    <row r="891" ht="15.75" customHeight="1"/>
-    <row r="892" ht="15.75" customHeight="1"/>
-    <row r="893" ht="15.75" customHeight="1"/>
-    <row r="894" ht="15.75" customHeight="1"/>
-    <row r="895" ht="15.75" customHeight="1"/>
-    <row r="896" ht="15.75" customHeight="1"/>
-    <row r="897" ht="15.75" customHeight="1"/>
-    <row r="898" ht="15.75" customHeight="1"/>
-    <row r="899" ht="15.75" customHeight="1"/>
-    <row r="900" ht="15.75" customHeight="1"/>
-    <row r="901" ht="15.75" customHeight="1"/>
-    <row r="902" ht="15.75" customHeight="1"/>
-    <row r="903" ht="15.75" customHeight="1"/>
-    <row r="904" ht="15.75" customHeight="1"/>
-    <row r="905" ht="15.75" customHeight="1"/>
-    <row r="906" ht="15.75" customHeight="1"/>
-    <row r="907" ht="15.75" customHeight="1"/>
-    <row r="908" ht="15.75" customHeight="1"/>
-    <row r="909" ht="15.75" customHeight="1"/>
-    <row r="910" ht="15.75" customHeight="1"/>
-    <row r="911" ht="15.75" customHeight="1"/>
-    <row r="912" ht="15.75" customHeight="1"/>
-    <row r="913" ht="15.75" customHeight="1"/>
-    <row r="914" ht="15.75" customHeight="1"/>
-    <row r="915" ht="15.75" customHeight="1"/>
-    <row r="916" ht="15.75" customHeight="1"/>
-    <row r="917" ht="15.75" customHeight="1"/>
-    <row r="918" ht="15.75" customHeight="1"/>
-    <row r="919" ht="15.75" customHeight="1"/>
-    <row r="920" ht="15.75" customHeight="1"/>
-    <row r="921" ht="15.75" customHeight="1"/>
-    <row r="922" ht="15.75" customHeight="1"/>
-    <row r="923" ht="15.75" customHeight="1"/>
-    <row r="924" ht="15.75" customHeight="1"/>
-    <row r="925" ht="15.75" customHeight="1"/>
-    <row r="926" ht="15.75" customHeight="1"/>
-    <row r="927" ht="15.75" customHeight="1"/>
-    <row r="928" ht="15.75" customHeight="1"/>
-    <row r="929" ht="15.75" customHeight="1"/>
-    <row r="930" ht="15.75" customHeight="1"/>
-    <row r="931" ht="15.75" customHeight="1"/>
-    <row r="932" ht="15.75" customHeight="1"/>
-    <row r="933" ht="15.75" customHeight="1"/>
-    <row r="934" ht="15.75" customHeight="1"/>
-    <row r="935" ht="15.75" customHeight="1"/>
-    <row r="936" ht="15.75" customHeight="1"/>
-    <row r="937" ht="15.75" customHeight="1"/>
-    <row r="938" ht="15.75" customHeight="1"/>
-    <row r="939" ht="15.75" customHeight="1"/>
-    <row r="940" ht="15.75" customHeight="1"/>
-    <row r="941" ht="15.75" customHeight="1"/>
-    <row r="942" ht="15.75" customHeight="1"/>
-    <row r="943" ht="15.75" customHeight="1"/>
-    <row r="944" ht="15.75" customHeight="1"/>
-    <row r="945" ht="15.75" customHeight="1"/>
-    <row r="946" ht="15.75" customHeight="1"/>
-    <row r="947" ht="15.75" customHeight="1"/>
-    <row r="948" ht="15.75" customHeight="1"/>
-    <row r="949" ht="15.75" customHeight="1"/>
-    <row r="950" ht="15.75" customHeight="1"/>
-    <row r="951" ht="15.75" customHeight="1"/>
-    <row r="952" ht="15.75" customHeight="1"/>
-    <row r="953" ht="15.75" customHeight="1"/>
-    <row r="954" ht="15.75" customHeight="1"/>
-    <row r="955" ht="15.75" customHeight="1"/>
-    <row r="956" ht="15.75" customHeight="1"/>
-    <row r="957" ht="15.75" customHeight="1"/>
-    <row r="958" ht="15.75" customHeight="1"/>
-    <row r="959" ht="15.75" customHeight="1"/>
-    <row r="960" ht="15.75" customHeight="1"/>
-    <row r="961" ht="15.75" customHeight="1"/>
-    <row r="962" ht="15.75" customHeight="1"/>
-    <row r="963" ht="15.75" customHeight="1"/>
-    <row r="964" ht="15.75" customHeight="1"/>
-    <row r="965" ht="15.75" customHeight="1"/>
-    <row r="966" ht="15.75" customHeight="1"/>
-    <row r="967" ht="15.75" customHeight="1"/>
-    <row r="968" ht="15.75" customHeight="1"/>
-    <row r="969" ht="15.75" customHeight="1"/>
-    <row r="970" ht="15.75" customHeight="1"/>
-    <row r="971" ht="15.75" customHeight="1"/>
-    <row r="972" ht="15.75" customHeight="1"/>
-    <row r="973" ht="15.75" customHeight="1"/>
-    <row r="974" ht="15.75" customHeight="1"/>
-    <row r="975" ht="15.75" customHeight="1"/>
-    <row r="976" ht="15.75" customHeight="1"/>
-    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="62" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="63" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="64" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <autoFilter ref="$A$1:$AR$66"/>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <autoFilter ref="A1:AR61" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{e0793d39-0939-496d-b129-198edd916feb}" enabled="0" method="" siteId="{e0793d39-0939-496d-b129-198edd916feb}" removed="1"/>
+</clbl:labelList>
 </file>